--- a/logical_radar.xlsx
+++ b/logical_radar.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fox\OneDrive\Desktop\software_arch\RemoteHealthMonitoring\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fox\OneDrive\Desktop\Universita'\Corsi\software_arch\RemoteHealthMonitoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90087A6A-85B5-4E90-BF21-0D47CBDD8AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0C0944-4D94-4418-9329-1F30E1738E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{B6302E51-422F-4DAB-BB14-BB736057E43B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="95">
   <si>
     <t>Astrazione</t>
   </si>
@@ -167,9 +167,6 @@
     <t>Attività Raw</t>
   </si>
   <si>
-    <t>Stima: 4/10</t>
-  </si>
-  <si>
     <t>3 on 10</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>Intensità: {L, M, H}</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>Low</t>
   </si>
   <si>
@@ -299,9 +293,6 @@
     <t>Situazione simmetrica della componente A</t>
   </si>
   <si>
-    <t>Il problema è presente solo se il medico modifica il piano di riabilitazione nel momento in cui D esegue controllo svolgimento ADL</t>
-  </si>
-  <si>
     <t>locale (R), ADL giornaliere (R), centrale (R/W)</t>
   </si>
   <si>
@@ -314,34 +305,22 @@
     <t>centrale (R/W), Medico di Turno (R/W)</t>
   </si>
   <si>
-    <t>L/M</t>
-  </si>
-  <si>
-    <t>Il problema è presente solo se il medico modifica il piano di riabilitazione nel momento in cui F esegue Controllo Piano di Riabilitazione</t>
-  </si>
-  <si>
     <t>A (datastore centrale)</t>
   </si>
   <si>
-    <t>G (datastore centrale)</t>
-  </si>
-  <si>
-    <t>Il conflitto sullo Storico Attività Riabilitazione ha probabilità alta di succedere ma non è impattante sul sistema in quanto il medico non accede agli ultimi dati raccolti, ma ha comunque a disposizione quelli precedenti. Invece i conflitti sul Piano di Riabilitazione hanno probabilità bassa di accadere</t>
-  </si>
-  <si>
     <t>C/G (datastore centrale)</t>
   </si>
   <si>
     <t>Il conflitto con C avviene quando C legge prima che A abbia scritto i dati rilevati: questo non succede mai se la frequenza con cui vengono rilevati i dati rimane 30 secondi. Il conflitto con G è simmetrico a quanto scritto per G</t>
   </si>
   <si>
-    <t>D/F (datastore centrale), A (datastore centrale)</t>
-  </si>
-  <si>
     <t>Perché quasi tutto i conflitti individuati riguardano dati non aggiornati</t>
   </si>
   <si>
     <t>e non la scrittura di dati che si stanno leggendo</t>
+  </si>
+  <si>
+    <t>Il conflitto sullo Storico Attività Riabilitazione ha probabilità alta di succedere ma non è impattante sul sistema in quanto il medico non accede agli ultimi dati raccolti, ma ha comunque a disposizione quelli precedenti.</t>
   </si>
 </sst>
 </file>
@@ -553,15 +532,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -574,7 +545,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -716,7 +695,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>3</c:v>
@@ -1879,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1926,16 +1905,16 @@
       <c r="B11" s="2"/>
     </row>
     <row r="20" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="19"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="17"/>
     </row>
     <row r="21" spans="3:10" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C21" s="5" t="s">
@@ -2143,9 +2122,9 @@
       <c r="G31" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
     </row>
     <row r="32" spans="3:10" x14ac:dyDescent="0.35">
       <c r="C32" s="3" t="s">
@@ -2166,22 +2145,22 @@
         <v>2.3809523809523801E-2</v>
       </c>
       <c r="H32" s="4"/>
-      <c r="I32" s="16" t="s">
+      <c r="I32" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="J32" s="16"/>
+      <c r="J32" s="14"/>
     </row>
     <row r="35" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C35" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
+      <c r="C35" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
     </row>
     <row r="36" spans="3:11" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C36" s="5" t="s">
@@ -2347,9 +2326,9 @@
       <c r="G42" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
     </row>
     <row r="43" spans="3:11" x14ac:dyDescent="0.35">
       <c r="C43" s="3" t="s">
@@ -2370,22 +2349,22 @@
         <v>0.14285714285714282</v>
       </c>
       <c r="H43" s="4"/>
-      <c r="I43" s="16" t="s">
+      <c r="I43" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="J43" s="16"/>
+      <c r="J43" s="14"/>
     </row>
     <row r="46" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
     </row>
     <row r="47" spans="3:11" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C47" s="5" t="s">
@@ -2554,9 +2533,9 @@
       <c r="G54" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="19"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.35">
       <c r="C55" s="3" t="s">
@@ -2577,22 +2556,22 @@
         <v>0.17857142857142858</v>
       </c>
       <c r="H55" s="4"/>
-      <c r="I55" s="16" t="s">
+      <c r="I55" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="J55" s="16"/>
+      <c r="J55" s="14"/>
     </row>
     <row r="58" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
     </row>
     <row r="59" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C59" s="5" t="s">
@@ -2640,12 +2619,8 @@
       <c r="C61" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D61" s="3">
-        <v>1</v>
-      </c>
-      <c r="E61" s="3">
-        <v>1</v>
-      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
       <c r="F61" s="3">
         <v>1</v>
       </c>
@@ -2655,9 +2630,7 @@
       <c r="H61" s="3">
         <v>1</v>
       </c>
-      <c r="I61" s="3">
-        <v>1</v>
-      </c>
+      <c r="I61" s="3"/>
       <c r="J61" s="3">
         <v>1</v>
       </c>
@@ -2686,11 +2659,11 @@
       </c>
       <c r="D63" s="5">
         <f>SUM(D60:D62)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="5">
         <f t="shared" ref="E63" si="11">SUM(E60:E62)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" s="5">
         <f t="shared" ref="F63" si="12">SUM(F60:F62)</f>
@@ -2706,7 +2679,7 @@
       </c>
       <c r="I63" s="5">
         <f t="shared" ref="I63" si="15">SUM(I60:I62)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" s="5">
         <f t="shared" ref="J63" si="16">SUM(J60:J62)</f>
@@ -2719,11 +2692,11 @@
       </c>
       <c r="D64" s="8">
         <f>D63/3</f>
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E64" s="8">
         <f t="shared" ref="E64" si="17">E63/3</f>
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="F64" s="8">
         <f t="shared" ref="F64" si="18">F63/3</f>
@@ -2739,7 +2712,7 @@
       </c>
       <c r="I64" s="8">
         <f t="shared" ref="I64" si="21">I63/3</f>
-        <v>0.66666666666666663</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="J64" s="8">
         <f t="shared" ref="J64" si="22">J63/3</f>
@@ -2760,9 +2733,9 @@
       <c r="G65" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19"/>
     </row>
     <row r="66" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C66" s="3" t="s">
@@ -2776,17 +2749,17 @@
       </c>
       <c r="F66" s="3">
         <f>AVERAGE(D64:J64)</f>
-        <v>0.5714285714285714</v>
+        <v>0.42857142857142849</v>
       </c>
       <c r="G66" s="9">
         <f>(F66-D66)/(E66-D66)</f>
-        <v>0.3571428571428571</v>
+        <v>0.14285714285714274</v>
       </c>
       <c r="H66" s="4"/>
-      <c r="I66" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="J66" s="16"/>
+      <c r="I66" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="J66" s="14"/>
     </row>
     <row r="68" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C68" s="3" t="s">
@@ -2794,11 +2767,11 @@
       </c>
     </row>
     <row r="69" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C69" s="20" t="s">
-        <v>44</v>
+      <c r="C69" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="D69" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="3:14" x14ac:dyDescent="0.35">
@@ -2808,33 +2781,33 @@
     </row>
     <row r="72" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C72" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73" spans="3:14" x14ac:dyDescent="0.35">
       <c r="K73" s="3"/>
       <c r="L73" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="N73" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="M73" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N73" s="3" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="74" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C74" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N74" s="3">
         <v>1</v>
@@ -2842,16 +2815,16 @@
     </row>
     <row r="75" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C75" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L75" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M75" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="M75" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="N75" s="3">
         <v>1</v>
@@ -2859,13 +2832,13 @@
     </row>
     <row r="76" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C76" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M76" s="3"/>
       <c r="N76" s="3">
@@ -2874,10 +2847,10 @@
     </row>
     <row r="77" spans="3:14" x14ac:dyDescent="0.35">
       <c r="K77" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M77" s="3"/>
       <c r="N77" s="3">
@@ -2886,13 +2859,13 @@
     </row>
     <row r="78" spans="3:14" x14ac:dyDescent="0.35">
       <c r="K78" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L78" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="M78" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="M78" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="N78" s="3">
         <v>3</v>
@@ -2900,13 +2873,13 @@
     </row>
     <row r="79" spans="3:14" x14ac:dyDescent="0.35">
       <c r="K79" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L79" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M79" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="M79" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="N79" s="3">
         <v>1</v>
@@ -2914,13 +2887,13 @@
     </row>
     <row r="80" spans="3:14" x14ac:dyDescent="0.35">
       <c r="K80" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L80" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="M80" s="3" t="s">
         <v>58</v>
-      </c>
-      <c r="M80" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="N80" s="3">
         <v>1</v>
@@ -2933,30 +2906,30 @@
     </row>
     <row r="83" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C83" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K84" s="3"/>
       <c r="L84" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M84" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="N84" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="N84" s="3" t="s">
+      <c r="O84" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="O84" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="85" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K85" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M85" s="3"/>
       <c r="N85" s="3">
@@ -2966,10 +2939,10 @@
     </row>
     <row r="86" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K86" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M86" s="3"/>
       <c r="N86" s="3">
@@ -2979,27 +2952,27 @@
     </row>
     <row r="87" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K87" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M87" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="L87" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M87" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="N87" s="3">
         <v>1</v>
       </c>
       <c r="O87" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K88" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M88" s="3"/>
       <c r="N88" s="3">
@@ -3009,13 +2982,13 @@
     </row>
     <row r="89" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K89" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -3024,10 +2997,10 @@
     </row>
     <row r="90" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K90" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M90" s="3"/>
       <c r="N90" s="3">
@@ -3037,10 +3010,10 @@
     </row>
     <row r="91" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K91" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L91" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M91" s="3"/>
       <c r="N91" s="3">
@@ -3055,68 +3028,68 @@
     </row>
     <row r="94" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C94" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K95" s="3"/>
       <c r="L95" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="N95" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="O95" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="P95" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q95" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="O95" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="P95" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q95" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="96" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C96" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K96" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N96" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="O96" s="3">
         <v>2</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C97" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N97" s="3"/>
       <c r="O97" s="3">
@@ -3127,59 +3100,53 @@
     </row>
     <row r="98" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K98" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M98" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="N98" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="O98" s="3">
+        <v>1</v>
+      </c>
+      <c r="P98" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="N98" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="O98" s="3">
-        <v>1</v>
-      </c>
-      <c r="P98" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="Q98" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K99" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="N99" s="3" t="s">
-        <v>95</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N99" s="3"/>
       <c r="O99" s="3">
-        <v>1</v>
-      </c>
-      <c r="P99" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q99" s="3" t="s">
-        <v>87</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+      <c r="Q99" s="3"/>
     </row>
     <row r="100" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K100" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="N100" s="3"/>
       <c r="O100" s="3">
@@ -3187,53 +3154,47 @@
       </c>
       <c r="P100" s="3"/>
       <c r="Q100" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="101" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K101" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>95</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="N101" s="3"/>
       <c r="O101" s="3">
-        <v>1</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>93</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P101" s="3"/>
+      <c r="Q101" s="3"/>
     </row>
     <row r="102" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K102" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="O102" s="3">
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="Q102" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="104" spans="3:17" x14ac:dyDescent="0.35">
@@ -3243,30 +3204,30 @@
     </row>
     <row r="105" spans="3:17" x14ac:dyDescent="0.35">
       <c r="C105" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="106" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K106" s="3"/>
       <c r="L106" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M106" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="N106" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="N106" s="3" t="s">
+      <c r="O106" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="O106" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="107" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K107" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M107" s="3"/>
       <c r="N107" s="3">
@@ -3276,10 +3237,10 @@
     </row>
     <row r="108" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K108" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M108" s="3"/>
       <c r="N108" s="3">
@@ -3289,27 +3250,27 @@
     </row>
     <row r="109" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K109" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L109" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M109" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="L109" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M109" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="N109" s="3">
         <v>1</v>
       </c>
       <c r="O109" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="110" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K110" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M110" s="3"/>
       <c r="N110" s="3">
@@ -3319,13 +3280,13 @@
     </row>
     <row r="111" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K111" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M111" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N111" s="3">
         <v>0</v>
@@ -3334,10 +3295,10 @@
     </row>
     <row r="112" spans="3:17" x14ac:dyDescent="0.35">
       <c r="K112" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L112" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M112" s="3"/>
       <c r="N112" s="3">
@@ -3347,10 +3308,10 @@
     </row>
     <row r="113" spans="11:15" x14ac:dyDescent="0.35">
       <c r="K113" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L113" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M113" s="3"/>
       <c r="N113" s="3">
@@ -3379,18 +3340,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3526,14 +3487,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{710FDD1C-F085-481C-95F4-8850306CEEEF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A5C0A887-D98D-4011-B0B0-E045215B38BE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3545,6 +3498,14 @@
     <ds:schemaRef ds:uri="bb9a0474-075b-4bdf-8fb1-ae2bb252bd11"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{710FDD1C-F085-481C-95F4-8850306CEEEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
